--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2220,6 +2220,122 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122582279</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105737</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>225197</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Äkta ljungsnärja</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Cuscuta epithymum var. epithymum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lummelunds bruk, 1 km N, Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>702708</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6405727</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lummelunda</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>I-Got-1949</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>1989-08-11</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1989-08-11</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gräsmark.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sofia Lund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122582279</v>
       </c>
       <c r="B15" t="n">
-        <v>105737</v>
+        <v>105740</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122582279</v>
       </c>
       <c r="B15" t="n">
-        <v>105740</v>
+        <v>105741</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122582279</v>
       </c>
       <c r="B15" t="n">
-        <v>105741</v>
+        <v>105744</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122582279</v>
       </c>
       <c r="B15" t="n">
-        <v>105744</v>
+        <v>105847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122582279</v>
       </c>
       <c r="B15" t="n">
-        <v>105847</v>
+        <v>105855</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122582279</v>
       </c>
       <c r="B15" t="n">
-        <v>105855</v>
+        <v>105857</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -2225,7 +2225,7 @@
         <v>122582279</v>
       </c>
       <c r="B15" t="n">
-        <v>105857</v>
+        <v>105865</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 17739-2024 artfynd.xlsx
+++ b/artfynd/A 17739-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2220,122 +2220,6 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>122582279</v>
-      </c>
-      <c r="B15" t="n">
-        <v>105865</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>225197</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Äkta ljungsnärja</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Cuscuta epithymum var. epithymum</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Lummelunds bruk, 1 km N, Gtl</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>702708</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6405727</v>
-      </c>
-      <c r="S15" t="n">
-        <v>50</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Gotland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Lummelunda</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>I-Got-1949</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>1989-08-11</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>1989-08-11</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Gräsmark.</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Sofia Lund</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Jörgen Petersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
